--- a/eciML1515/data/UnconstrainedMaxGrowth.xlsx
+++ b/eciML1515/data/UnconstrainedMaxGrowth.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\ECOMAP\ECOMAP\eciML1515\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCB730F-43B8-484A-AFE2-8EF1C183EB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C680E7C-DEEE-4495-BFA6-2F2FEBE6B7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13530" yWindow="5280" windowWidth="28800" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4890" yWindow="2460" windowWidth="28800" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -105,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BIOMASS_Ec_iML1515_core_75p37M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EX_o2_e</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -162,6 +158,10 @@
   </si>
   <si>
     <t>EX_pyr_e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biomass</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,37 +504,37 @@
         <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -545,37 +545,37 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1">
         <v>0.74</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -586,37 +586,37 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1">
         <v>0.52</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -627,37 +627,37 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1">
         <v>0.30499999999999999</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -668,37 +668,37 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1">
         <v>0.61</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -709,37 +709,37 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1">
         <v>0.47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -750,37 +750,37 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1">
         <v>0.24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -791,37 +791,37 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1">
         <v>0.24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -829,40 +829,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1">
         <v>0.41</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -873,37 +873,37 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>0.54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -914,37 +914,37 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1">
         <v>0.37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -955,37 +955,37 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1">
         <v>0.47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -996,37 +996,37 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1">
         <v>0.41</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -1037,37 +1037,37 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1">
         <v>0.24</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -1078,37 +1078,37 @@
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1">
         <v>0.41</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -1119,37 +1119,37 @@
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>0.68</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -1160,37 +1160,37 @@
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1">
         <v>0.48</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -1201,37 +1201,37 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1">
         <v>0.4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -1242,37 +1242,37 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -1283,37 +1283,37 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="1">
         <v>0.51</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -1324,37 +1324,37 @@
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>0.78</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -1365,37 +1365,37 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" s="1">
         <v>0.61</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -1406,37 +1406,37 @@
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="1">
         <v>0.48</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
@@ -1447,37 +1447,37 @@
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1">
         <v>0.38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -1488,37 +1488,37 @@
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" s="1">
         <v>0.51</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
